--- a/isms-core-framework/A.8-technological-controls/isms-a.8.9-configuration-management/WKBK/90_workbooks/ISMS_A_8_9_4_Security_Hardening_Assessment_20260208.xlsx
+++ b/isms-core-framework/A.8-technological-controls/isms-a.8.9-configuration-management/WKBK/90_workbooks/ISMS_A_8_9_4_Security_Hardening_Assessment_20260208.xlsx
@@ -812,7 +812,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>08.02.2026 11:50</t>
+          <t>08.02.2026 12:26</t>
         </is>
       </c>
     </row>
